--- a/Cell data Sara DU145/2026_03_19/2026_03_19.xlsx
+++ b/Cell data Sara DU145/2026_03_19/2026_03_19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_19\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649433EF-5465-4A95-92D5-CF075C8EAECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47494959-5427-4E8A-8917-CBEA15994B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="9">
   <si>
-    <t>Radiation</t>
-  </si>
-  <si>
     <t>Experiment</t>
   </si>
   <si>
@@ -39,19 +36,22 @@
     <t>Dose</t>
   </si>
   <si>
-    <t>Flask number</t>
-  </si>
-  <si>
     <t>Cells plated</t>
-  </si>
-  <si>
-    <t>Colonies</t>
   </si>
   <si>
     <t>Proton LL</t>
   </si>
   <si>
     <t>Proton HL</t>
+  </si>
+  <si>
+    <t>Rad</t>
+  </si>
+  <si>
+    <t>Triplicate</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -535,8 +535,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
@@ -863,715 +862,715 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1.3</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>250</v>
+      </c>
+      <c r="G2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1.3</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>250</v>
+      </c>
+      <c r="G3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1.3</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>250</v>
+      </c>
+      <c r="G4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1.3</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>250</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1.3</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>250</v>
+      </c>
+      <c r="G6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1.3</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="F7">
+        <v>250</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
         <v>1.3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>500</v>
+      </c>
+      <c r="G8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>1.3</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="G9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>1.3</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>500</v>
+      </c>
+      <c r="G10">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1.3</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>2000</v>
+      </c>
+      <c r="G11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>1.3</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>2000</v>
+      </c>
+      <c r="G12">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>1.3</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>2000</v>
+      </c>
+      <c r="G13">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>1.3</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>5000</v>
+      </c>
+      <c r="G14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>1.3</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>5000</v>
+      </c>
+      <c r="G15">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>1.3</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>5000</v>
+      </c>
+      <c r="G16">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>16.5</v>
+      </c>
+      <c r="D17">
         <v>0</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F17">
         <v>250</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G17">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D3" s="1">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>16.5</v>
+      </c>
+      <c r="D18">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E18">
         <v>2</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F18">
         <v>250</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G18">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D4" s="1">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>16.5</v>
+      </c>
+      <c r="D19">
         <v>0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E19">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F19">
         <v>250</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G19">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D5" s="1">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>16.5</v>
+      </c>
+      <c r="D20">
         <v>0</v>
       </c>
-      <c r="E5" s="1">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
         <v>250</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G20">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D6" s="1">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>16.5</v>
+      </c>
+      <c r="D21">
         <v>0</v>
       </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
         <v>250</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G21">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D7" s="1">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>16.5</v>
+      </c>
+      <c r="D22">
         <v>0</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E22">
         <v>6</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F22">
         <v>250</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G22">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D8" s="1">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>16.5</v>
+      </c>
+      <c r="D23">
         <v>2</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E23">
         <v>1</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F23">
         <v>500</v>
       </c>
-      <c r="G8" s="1">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="G23">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>16.5</v>
+      </c>
+      <c r="D24">
         <v>2</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E24">
         <v>2</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F24">
         <v>500</v>
       </c>
-      <c r="G9" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="G24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>16.5</v>
+      </c>
+      <c r="D25">
         <v>2</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E25">
         <v>3</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F25">
         <v>500</v>
       </c>
-      <c r="G10" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="G25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>16.5</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F26">
         <v>2000</v>
       </c>
-      <c r="G11" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>16.5</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
         <v>2</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F27">
         <v>2000</v>
       </c>
-      <c r="G12" s="1">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>8</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D13" s="1">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="G27">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>16.5</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
         <v>3</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F28">
         <v>2000</v>
       </c>
-      <c r="G13" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D14" s="1">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="G28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>16.5</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
         <v>1</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F29">
         <v>5000</v>
       </c>
-      <c r="G14" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="1">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>16.5</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30">
         <v>2</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F30">
         <v>5000</v>
       </c>
-      <c r="G15" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="D16" s="1">
-        <v>8</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>16.5</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
         <v>3</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F31">
         <v>5000</v>
       </c>
-      <c r="G16" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="1">
-        <v>8</v>
-      </c>
-      <c r="C17" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>250</v>
-      </c>
-      <c r="G17" s="1">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="1">
-        <v>8</v>
-      </c>
-      <c r="C18" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1">
-        <v>250</v>
-      </c>
-      <c r="G18" s="1">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="1">
-        <v>8</v>
-      </c>
-      <c r="C19" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
-        <v>3</v>
-      </c>
-      <c r="F19" s="1">
-        <v>250</v>
-      </c>
-      <c r="G19" s="1">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1">
-        <v>8</v>
-      </c>
-      <c r="C20" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1">
-        <v>4</v>
-      </c>
-      <c r="F20" s="1">
-        <v>250</v>
-      </c>
-      <c r="G20" s="1">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1">
-        <v>8</v>
-      </c>
-      <c r="C21" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>250</v>
-      </c>
-      <c r="G21" s="1">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="1">
-        <v>8</v>
-      </c>
-      <c r="C22" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D22" s="1">
-        <v>0</v>
-      </c>
-      <c r="E22" s="1">
-        <v>6</v>
-      </c>
-      <c r="F22" s="1">
-        <v>250</v>
-      </c>
-      <c r="G22" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="1">
-        <v>8</v>
-      </c>
-      <c r="C23" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>500</v>
-      </c>
-      <c r="G23" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="1">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="F24" s="1">
-        <v>500</v>
-      </c>
-      <c r="G24" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="1">
-        <v>8</v>
-      </c>
-      <c r="C25" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1">
-        <v>3</v>
-      </c>
-      <c r="F25" s="1">
-        <v>500</v>
-      </c>
-      <c r="G25" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="1">
-        <v>8</v>
-      </c>
-      <c r="C26" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D26" s="1">
-        <v>5</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="1">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D27" s="1">
-        <v>5</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G27" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D28" s="1">
-        <v>5</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G28" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="1">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D29" s="1">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="1">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D30" s="1">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G30" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="1">
-        <v>8</v>
-      </c>
-      <c r="C31" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="D31" s="1">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G31" s="1">
+      <c r="G31">
         <v>8</v>
       </c>
     </row>

--- a/Cell data Sara DU145/2026_03_19/2026_03_19.xlsx
+++ b/Cell data Sara DU145/2026_03_19/2026_03_19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_19\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47494959-5427-4E8A-8917-CBEA15994B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BD046B-CF7D-44E8-A342-41287F65C54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="10">
   <si>
     <t>Experiment</t>
   </si>
@@ -39,12 +39,6 @@
     <t>Cells plated</t>
   </si>
   <si>
-    <t>Proton LL</t>
-  </si>
-  <si>
-    <t>Proton HL</t>
-  </si>
-  <si>
     <t>Rad</t>
   </si>
   <si>
@@ -52,6 +46,15 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>Proton L</t>
+  </si>
+  <si>
+    <t>Proton H</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -858,12 +861,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -875,18 +878,18 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>8</v>
@@ -909,7 +912,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>8</v>
@@ -932,7 +935,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -955,7 +958,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -978,7 +981,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -1001,7 +1004,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -1024,7 +1027,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>8</v>
@@ -1047,7 +1050,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1070,7 +1073,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>8</v>
@@ -1093,7 +1096,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -1116,7 +1119,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>8</v>
@@ -1139,7 +1142,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>8</v>
@@ -1162,7 +1165,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -1185,7 +1188,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -1208,7 +1211,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -1231,7 +1234,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>8</v>
@@ -1240,21 +1243,21 @@
         <v>16.5</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G17">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -1263,21 +1266,21 @@
         <v>16.5</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G18">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>8</v>
@@ -1286,21 +1289,21 @@
         <v>16.5</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="G19">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B20">
         <v>8</v>
@@ -1309,21 +1312,21 @@
         <v>16.5</v>
       </c>
       <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>2000</v>
+      </c>
+      <c r="G20">
         <v>0</v>
-      </c>
-      <c r="E20">
-        <v>4</v>
-      </c>
-      <c r="F20">
-        <v>250</v>
-      </c>
-      <c r="G20">
-        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21">
         <v>8</v>
@@ -1332,21 +1335,21 @@
         <v>16.5</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="G21">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B22">
         <v>8</v>
@@ -1355,21 +1358,21 @@
         <v>16.5</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="G22">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23">
         <v>8</v>
@@ -1378,21 +1381,21 @@
         <v>16.5</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G23">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24">
         <v>8</v>
@@ -1401,21 +1404,21 @@
         <v>16.5</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G24">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -1424,153 +1427,15 @@
         <v>16.5</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="F25">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G25">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26">
-        <v>8</v>
-      </c>
-      <c r="C26">
-        <v>16.5</v>
-      </c>
-      <c r="D26">
-        <v>5</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>2000</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27">
-        <v>8</v>
-      </c>
-      <c r="C27">
-        <v>16.5</v>
-      </c>
-      <c r="D27">
-        <v>5</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27">
-        <v>2000</v>
-      </c>
-      <c r="G27">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>16.5</v>
-      </c>
-      <c r="D28">
-        <v>5</v>
-      </c>
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28">
-        <v>2000</v>
-      </c>
-      <c r="G28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29">
-        <v>8</v>
-      </c>
-      <c r="C29">
-        <v>16.5</v>
-      </c>
-      <c r="D29">
-        <v>8</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>5000</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30">
-        <v>8</v>
-      </c>
-      <c r="C30">
-        <v>16.5</v>
-      </c>
-      <c r="D30">
-        <v>8</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="F30">
-        <v>5000</v>
-      </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31">
-        <v>8</v>
-      </c>
-      <c r="C31">
-        <v>16.5</v>
-      </c>
-      <c r="D31">
-        <v>8</v>
-      </c>
-      <c r="E31">
-        <v>3</v>
-      </c>
-      <c r="F31">
-        <v>5000</v>
-      </c>
-      <c r="G31">
         <v>8</v>
       </c>
     </row>
